--- a/inspection_forms/016_drainage_survey--inspection_forms.xlsx
+++ b/inspection_forms/016_drainage_survey--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>drainage_survey_1</t>
+          <t>Drainage System Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_the_drainage_system_status</t>
+          <t>Is there a leak in the drainage system?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>is_there_a_leak</t>
+          <t>Is there an obstruction in the drainage system?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_is_the_current_status_of_the_drainage_system</t>
+          <t>Current status of the drainage system</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>is_there_an_obstruction</t>
+          <t>Type of drainage system used</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_the_current_status_of_the_drainage_system</t>
+          <t>Drainage system inspection notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>is_there_an_obstruction</t>
+          <t>Drainage system inspection date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>is_there_an_obstruction</t>
+          <t>Drainage system inspection time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,11 +709,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_the_drainage_system_used</t>
+          <t>Is there any other issue with the drainage system?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>drainage_survey_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Any other comments about the drainage system?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>drainage_survey_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Is the drainage system properly maintained?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -733,7 +779,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -758,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drainage_survey_2_choices</t>
+          <t>drainage_survey_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -775,7 +821,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drainage_survey_2_choices</t>
+          <t>drainage_survey_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -792,7 +838,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drainage_survey_3_choices</t>
+          <t>drainage_survey_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,7 +855,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drainage_survey_3_choices</t>
+          <t>drainage_survey_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -826,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drainage_survey_5_choices</t>
+          <t>drainage_survey_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -843,7 +889,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drainage_survey_5_choices</t>
+          <t>drainage_survey_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -860,7 +906,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drainage_survey_7_choices</t>
+          <t>drainage_survey_9_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -877,7 +923,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drainage_survey_7_choices</t>
+          <t>drainage_survey_9_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -894,7 +940,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drainage_survey_8_choices</t>
+          <t>drainage_survey_11_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -911,7 +957,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drainage_survey_8_choices</t>
+          <t>drainage_survey_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
